--- a/scripts/data/research.xlsx
+++ b/scripts/data/research.xlsx
@@ -1,37 +1,100 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamilakolpashnikova/Dropbox/Mac/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CF3672-7DB9-4E42-BDC6-CCF604AF899A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Research" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t>format</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>Research Themes</t>
+  </si>
+  <si>
+    <t>theme</t>
+  </si>
+  <si>
+    <t>Health Informatics &amp; Clinical NLP</t>
+  </si>
+  <si>
+    <t>We develop natural language processing methods to extract insights from clinical notes, policy documents, and health records while addressing privacy, bias, and ethical use of AI in healthcare settings.</t>
+  </si>
+  <si>
+    <t>Big Data Analytics for Population Health</t>
+  </si>
+  <si>
+    <t>Our lab builds scalable analytics pipelines to support decision-making in complex health systems, including methods for integrating heterogeneous data sources and summarizing evidence for policymakers.</t>
+  </si>
+  <si>
+    <t>Modelling Complex Health Systems</t>
+  </si>
+  <si>
+    <t>We use agent-based simulation and computational modelling to study systemic challenges such as homelessness, obesity, and access to care, helping stakeholders evaluate interventions before deployment.</t>
+  </si>
+  <si>
+    <t>Current Projects</t>
+  </si>
+  <si>
+    <t>list</t>
+  </si>
+  <si>
+    <t>Health Systems Simulation</t>
+  </si>
+  <si>
+    <t>Agent-based models for policy evaluation and resource allocation.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,81 +113,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,192 +416,88 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="90" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="90" customWidth="1"/>
+    <col min="5" max="5" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>section</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>format</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Research Themes</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>theme</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Health Informatics &amp; Clinical NLP</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>We develop natural language processing methods to extract insights from clinical notes, policy documents, and health records while addressing privacy, bias, and ethical use of AI in healthcare settings.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Research Themes</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>theme</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Big Data Analytics for Population Health</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Our lab builds scalable analytics pipelines to support decision-making in complex health systems, including methods for integrating heterogeneous data sources and summarizing evidence for policymakers.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Research Themes</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>theme</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Modelling Complex Health Systems</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>We use agent-based simulation and computational modelling to study systemic challenges such as homelessness, obesity, and access to care, helping stakeholders evaluate interventions before deployment.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Current Projects</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>HEAL-Summ</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Frameworks for health information summarization and evidence synthesis.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://github.com/heal-lab/heal-summ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Current Projects</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ethical LLMs in Healthcare</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Studying fairness, transparency, and governance of large language models in clinical contexts.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Current Projects</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Health Systems Simulation</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Agent-based models for policy evaluation and resource allocation.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://github.com/heal-lab/health-systems-simulation</t>
-        </is>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/data/research.xlsx
+++ b/scripts/data/research.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamilakolpashnikova/Dropbox/Mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CF3672-7DB9-4E42-BDC6-CCF604AF899A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55043CA-CABC-2C4F-A651-E2AF52D69B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39380" yWindow="640" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>section</t>
   </si>
@@ -67,10 +67,45 @@
     <t>list</t>
   </si>
   <si>
-    <t>Health Systems Simulation</t>
-  </si>
-  <si>
-    <t>Agent-based models for policy evaluation and resource allocation.</t>
+    <t>The CCSA Social Reporting Tool is a national platform built by the Canadian Centre on Substance Use and Addiction in collaboration with York University's HEAL Lab. It tracks hundreds of trusted social media accounts across every province and territory, uses AI to classify events, and maps what it finds to show emerging trends in drug supply, public safety, and public health. Results appear on an interactive map and dashboard, in English and French. Leaders in health, policy, and community safety can use it to get a single, current view of emerging risks.</t>
+  </si>
+  <si>
+    <t>CCSA Dashboard</t>
+  </si>
+  <si>
+    <t>Dr Fu’s current research examines neurological and mental health risks among people experiencing homelessness. Using administrative and community-level data, including the Homeless Individuals and Families Information System (HIFIS) and Point-in-Time Count data, his work investigates patterns of mental health needs, health disparities, and associated social and health-related risk factors. This research aims to generate evidence that can support more informed service planning, public health interventions, and policy responses for people experiencing homelessness and other underserved populations.</t>
+  </si>
+  <si>
+    <t>Health Risks of Homelessness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am currently researching AI-supported clinical decision-making in mental health, focusing on how clinicians calibrate trust in AI recommendations and when they accept, modify, or override AI advice. This work also considers how individual decisions may translate into broader health-system outcomes, including equity, resource utilization, and patient flow. In parallel, I am contributing to research involving Thunder Bay HIFIS (Homeless Individuals and Families Information System) and the analysis of online Reddit data to better understand homelessness, associated stigma, service coordination, and system-level decision-making.
+</t>
+  </si>
+  <si>
+    <t>Human-AI Interaction</t>
+  </si>
+  <si>
+    <t>Multilingual Conversational Health AI for Older Adults Using Small Language Models:
+I am developing multilingual conversational health AI for older adults, using small language models (SLMs) that run locally on consumer devices rather than relying on cloud APIs. The work focuses on heritage and minority language speakers in the Greater Toronto Area, with an initial language set of Cantonese, Mandarin, Punjabi, Spanish, Tagalog, Hindi, Tamil, and Farsi. The project spans a systematic review of the current landscape, a benchmark evaluation of SLMs across these eight languages, a working prototype, and a co-designed evaluation framework developed with older adults and community partners. Because on-device inference keeps health conversations private by design, the approach also addresses the accountability and data-governance concerns that limit adoption of commercial assistants in Ontario care settings.</t>
+  </si>
+  <si>
+    <t>Multilingual Conversational Health AI</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Kamila Kolpashnikova</t>
+  </si>
+  <si>
+    <t>Frederic Fu</t>
+  </si>
+  <si>
+    <t>Debanjan Borthakur</t>
+  </si>
+  <si>
+    <t>Arunim Garg</t>
   </si>
 </sst>
 </file>
@@ -92,15 +127,21 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -108,13 +149,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -425,9 +479,10 @@
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="90" customWidth="1"/>
     <col min="5" max="5" width="45" customWidth="1"/>
+    <col min="6" max="6" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -443,8 +498,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -458,7 +516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -472,7 +530,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -486,7 +544,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -494,10 +552,64 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
-        <v>16</v>
+      <c r="F5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/data/research.xlsx
+++ b/scripts/data/research.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamilakolpashnikova/Dropbox/Mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55043CA-CABC-2C4F-A651-E2AF52D69B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E28FC1-01E4-7A46-B474-D41CF3D65566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39380" yWindow="640" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,6 @@
     <t>name</t>
   </si>
   <si>
-    <t>Kamila Kolpashnikova</t>
-  </si>
-  <si>
     <t>Frederic Fu</t>
   </si>
   <si>
@@ -106,6 +103,9 @@
   </si>
   <si>
     <t>Arunim Garg</t>
+  </si>
+  <si>
+    <t>Mila Kolpashnikova</t>
   </si>
 </sst>
 </file>
@@ -558,7 +558,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -575,7 +575,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -592,7 +592,7 @@
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -609,7 +609,7 @@
         <v>21</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
